--- a/Hand_edited_log/1/student/cuongnvhe181200/TC2/GradeDetail.xlsx
+++ b/Hand_edited_log/1/student/cuongnvhe181200/TC2/GradeDetail.xlsx
@@ -1041,10 +1041,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P2" s="0">
-        <x:v>49693</x:v>
+        <x:v>51702</x:v>
       </x:c>
       <x:c r="Q2" s="0">
-        <x:v>4000</x:v>
+        <x:v>4003</x:v>
       </x:c>
       <x:c r="R2" s="2" t="s">
         <x:v>46</x:v>
@@ -1097,10 +1097,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P3" s="0">
-        <x:v>4000</x:v>
+        <x:v>4003</x:v>
       </x:c>
       <x:c r="Q3" s="0">
-        <x:v>49693</x:v>
+        <x:v>51702</x:v>
       </x:c>
       <x:c r="R3" s="2" t="s">
         <x:v>46</x:v>
@@ -1153,10 +1153,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P4" s="0">
-        <x:v>49693</x:v>
+        <x:v>51702</x:v>
       </x:c>
       <x:c r="Q4" s="0">
-        <x:v>4000</x:v>
+        <x:v>4003</x:v>
       </x:c>
       <x:c r="R4" s="2" t="s">
         <x:v>46</x:v>
@@ -1209,10 +1209,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P5" s="0">
-        <x:v>4000</x:v>
+        <x:v>4003</x:v>
       </x:c>
       <x:c r="Q5" s="0">
-        <x:v>49693</x:v>
+        <x:v>51702</x:v>
       </x:c>
       <x:c r="R5" s="3" t="s">
         <x:v>55</x:v>
@@ -1265,10 +1265,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P6" s="0">
-        <x:v>49693</x:v>
+        <x:v>51702</x:v>
       </x:c>
       <x:c r="Q6" s="0">
-        <x:v>4000</x:v>
+        <x:v>4003</x:v>
       </x:c>
       <x:c r="R6" s="3" t="s">
         <x:v>55</x:v>
@@ -1321,10 +1321,10 @@
         <x:v>58</x:v>
       </x:c>
       <x:c r="P7" s="0">
-        <x:v>49693</x:v>
+        <x:v>51702</x:v>
       </x:c>
       <x:c r="Q7" s="0">
-        <x:v>4000</x:v>
+        <x:v>4003</x:v>
       </x:c>
       <x:c r="R7" s="3" t="s">
         <x:v>55</x:v>
@@ -1377,10 +1377,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P8" s="0">
-        <x:v>4000</x:v>
+        <x:v>4003</x:v>
       </x:c>
       <x:c r="Q8" s="0">
-        <x:v>49693</x:v>
+        <x:v>51702</x:v>
       </x:c>
       <x:c r="R8" s="3" t="s">
         <x:v>55</x:v>
@@ -1433,10 +1433,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P9" s="0">
-        <x:v>49693</x:v>
+        <x:v>51702</x:v>
       </x:c>
       <x:c r="Q9" s="0">
-        <x:v>4000</x:v>
+        <x:v>4003</x:v>
       </x:c>
       <x:c r="R9" s="3" t="s">
         <x:v>55</x:v>
@@ -1489,10 +1489,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P10" s="0">
-        <x:v>4000</x:v>
+        <x:v>4003</x:v>
       </x:c>
       <x:c r="Q10" s="0">
-        <x:v>49693</x:v>
+        <x:v>51702</x:v>
       </x:c>
       <x:c r="R10" s="3" t="s">
         <x:v>55</x:v>
